--- a/backend/uploads/Sample_Products.xlsx
+++ b/backend/uploads/Sample_Products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NNPTUD_DoAn\backend\uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tranm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6C49A8-8CB4-44BC-9EDF-6A89A06EA048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EE9C431-EC15-43C7-921A-E3750169D068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="396">
   <si>
     <t>Tên SP</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Calatrava</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800, https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800</t>
-  </si>
-  <si>
     <t>female</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>Autavia</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800, https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800</t>
-  </si>
-  <si>
     <t>eco-drive</t>
   </si>
   <si>
@@ -133,9 +127,6 @@
     <t>Grand Complications</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800, https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800</t>
-  </si>
-  <si>
     <t>male</t>
   </si>
   <si>
@@ -160,9 +151,6 @@
     <t>Aquanaut</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800, https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800</t>
-  </si>
-  <si>
     <t>unisex</t>
   </si>
   <si>
@@ -190,9 +178,6 @@
     <t>Baby-G</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800, https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800</t>
-  </si>
-  <si>
     <t>CAS-BAB-7411</t>
   </si>
   <si>
@@ -208,9 +193,6 @@
     <t>Prospex</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800, https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800</t>
-  </si>
-  <si>
     <t>SEI-PRO-5221</t>
   </si>
   <si>
@@ -229,9 +211,6 @@
     <t>King Power</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800, https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800</t>
-  </si>
-  <si>
     <t>HUB-KIN-2870</t>
   </si>
   <si>
@@ -247,9 +226,6 @@
     <t>Royal Oak Offshore</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800, https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800</t>
-  </si>
-  <si>
     <t>AUD-ROY-3192</t>
   </si>
   <si>
@@ -259,9 +235,6 @@
     <t>Royal Oak</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800, https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800</t>
-  </si>
-  <si>
     <t>AUD-ROY-9210</t>
   </si>
   <si>
@@ -295,9 +268,6 @@
     <t>Edifice</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800, https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800</t>
-  </si>
-  <si>
     <t>CAS-EDI-7567</t>
   </si>
   <si>
@@ -310,9 +280,6 @@
     <t>Seastar</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800, https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800</t>
-  </si>
-  <si>
     <t>TIS-SEA-1078</t>
   </si>
   <si>
@@ -325,9 +292,6 @@
     <t>Aquaracer</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800, https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800</t>
-  </si>
-  <si>
     <t>TAG-AQU-6647</t>
   </si>
   <si>
@@ -346,9 +310,6 @@
     <t>Carson</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800, https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800</t>
-  </si>
-  <si>
     <t>TIS-CAR-5375</t>
   </si>
   <si>
@@ -376,9 +337,6 @@
     <t>Seamaster</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800, https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800</t>
-  </si>
-  <si>
     <t>OME-SEA-8455</t>
   </si>
   <si>
@@ -388,9 +346,6 @@
     <t>DolceVita</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800, https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800</t>
-  </si>
-  <si>
     <t>LON-DOL-2365</t>
   </si>
   <si>
@@ -403,9 +358,6 @@
     <t>Oyster Perpetual</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800, https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800</t>
-  </si>
-  <si>
     <t>ROL-OYS-6552</t>
   </si>
   <si>
@@ -415,9 +367,6 @@
     <t>Monaco</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800, https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800</t>
-  </si>
-  <si>
     <t>TAG-MON-4837</t>
   </si>
   <si>
@@ -427,9 +376,6 @@
     <t>De Ville</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800, https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800</t>
-  </si>
-  <si>
     <t>OME-DE -2446</t>
   </si>
   <si>
@@ -454,18 +400,12 @@
     <t>Spirit of Big Bang</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800, https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800</t>
-  </si>
-  <si>
     <t>HUB-SPI-2858</t>
   </si>
   <si>
     <t>TAG Heuer Monaco V6 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800, https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800</t>
-  </si>
-  <si>
     <t>TAG-MON-1973</t>
   </si>
   <si>
@@ -475,18 +415,12 @@
     <t>HydroConquest</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800, https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800</t>
-  </si>
-  <si>
     <t>LON-HYD-9258</t>
   </si>
   <si>
     <t>TAG Heuer Monaco V1 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800, https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800</t>
-  </si>
-  <si>
     <t>TAG-MON-2223</t>
   </si>
   <si>
@@ -508,9 +442,6 @@
     <t>Hublot Big Bang V5 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800, https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800</t>
-  </si>
-  <si>
     <t>HUB-BIG-5647</t>
   </si>
   <si>
@@ -529,9 +460,6 @@
     <t>Datejust</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800, https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800</t>
-  </si>
-  <si>
     <t>ROL-DAT-8642</t>
   </si>
   <si>
@@ -547,27 +475,18 @@
     <t>Audemars Piguet Code 11.59 V4 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800, https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800</t>
-  </si>
-  <si>
     <t>AUD-COD-5599</t>
   </si>
   <si>
     <t>Patek Philippe Calatrava V1 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800, https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800</t>
-  </si>
-  <si>
     <t>PAT-CAL-1564</t>
   </si>
   <si>
     <t>Seiko Prospex V10 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800, https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800</t>
-  </si>
-  <si>
     <t>SEI-PRO-6391</t>
   </si>
   <si>
@@ -577,9 +496,6 @@
     <t>5 Sports</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800, https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800</t>
-  </si>
-  <si>
     <t>SEI-5 S-3775</t>
   </si>
   <si>
@@ -589,9 +505,6 @@
     <t>Chemin des Tourelles</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800, https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800</t>
-  </si>
-  <si>
     <t>TIS-CHE-1230</t>
   </si>
   <si>
@@ -622,18 +535,12 @@
     <t>Vintage</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800, https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800</t>
-  </si>
-  <si>
     <t>CAS-VIN-1595</t>
   </si>
   <si>
     <t>Seiko Prospex V7 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800, https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800</t>
-  </si>
-  <si>
     <t>SEI-PRO-3177</t>
   </si>
   <si>
@@ -649,18 +556,12 @@
     <t>Omega De Ville V10 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800, https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800</t>
-  </si>
-  <si>
     <t>OME-DE -3115</t>
   </si>
   <si>
     <t>Casio Vintage V8 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800, https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800</t>
-  </si>
-  <si>
     <t>CAS-VIN-4440</t>
   </si>
   <si>
@@ -694,9 +595,6 @@
     <t>Hublot King Power V8 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800, https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800</t>
-  </si>
-  <si>
     <t>HUB-KIN-4610</t>
   </si>
   <si>
@@ -718,9 +616,6 @@
     <t>TAG Heuer Aquaracer V4 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800, https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800</t>
-  </si>
-  <si>
     <t>TAG-AQU-6000</t>
   </si>
   <si>
@@ -733,9 +628,6 @@
     <t>Patek Philippe Calatrava V9 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800, https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800</t>
-  </si>
-  <si>
     <t>PAT-CAL-5894</t>
   </si>
   <si>
@@ -757,9 +649,6 @@
     <t>Casio Vintage V1 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800, https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800</t>
-  </si>
-  <si>
     <t>CAS-VIN-8160</t>
   </si>
   <si>
@@ -799,9 +688,6 @@
     <t>Master Collection</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1548036328-c9fa89d128fa?w=800, https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800</t>
-  </si>
-  <si>
     <t>LON-MAS-9797</t>
   </si>
   <si>
@@ -847,9 +733,6 @@
     <t>Premier</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800, https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800</t>
-  </si>
-  <si>
     <t>SEI-PRE-2483</t>
   </si>
   <si>
@@ -871,9 +754,6 @@
     <t>Rolex Datejust V9 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1547996160-81dfa63595aa?w=800, https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800</t>
-  </si>
-  <si>
     <t>ROL-DAT-7414</t>
   </si>
   <si>
@@ -904,18 +784,12 @@
     <t>Omega De Ville V8 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800, https://images.unsplash.com/photo-1612817288484-6f916006741a?w=800</t>
-  </si>
-  <si>
     <t>OME-DE -5092</t>
   </si>
   <si>
     <t>Audemars Piguet Royal Oak V5 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800, https://images.unsplash.com/photo-1523170335258-f5ed11844a49?w=800</t>
-  </si>
-  <si>
     <t>AUD-ROY-4286</t>
   </si>
   <si>
@@ -1003,9 +877,6 @@
     <t>Audemars Piguet Royal Oak V2 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1587836374828-bc36224151b7?w=800, https://images.unsplash.com/photo-1622312675662-87063ed00888?w=800</t>
-  </si>
-  <si>
     <t>AUD-ROY-3842</t>
   </si>
   <si>
@@ -1027,9 +898,6 @@
     <t>Longines HydroConquest V1 Edition</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800, https://images.unsplash.com/photo-1614164185128-e4ec99c436d7?w=800</t>
-  </si>
-  <si>
     <t>LON-HYD-4717</t>
   </si>
   <si>
@@ -1061,6 +929,285 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778947/luxury-watch-store/g4minbb1pehlanwgzsr4.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778945/luxury-watch-store/thmkjz2exy5rwuqmbf7s.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778944/luxury-watch-store/kdu3yle0dairs0ktzgez.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778942/luxury-watch-store/idgieaibcokfywun5dq7.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778941/luxury-watch-store/s0skgke3fbrehuv3rktr.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778940/luxury-watch-store/ybh6csea138sxoku4vsz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778938/luxury-watch-store/kq1ibpkndpkc3x55lpsr.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778937/luxury-watch-store/xh9htkcqp2yv1ugqc6kg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778936/luxury-watch-store/au3wiuivjv1fhrw8bzwp.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778934/luxury-watch-store/gyl7bu4etafqthuvku1c.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778933/luxury-watch-store/w8bqunzca6ntm5lwc6ek.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778932/luxury-watch-store/sfjd1iyspsve2uid5tsk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778929/luxury-watch-store/scdzzejmytcvbrfgq1ww.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778925/luxury-watch-store/ejeizuuykiuytg0hqr1m.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778924/luxury-watch-store/qbsxbzmgisqguehzydbn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778922/luxury-watch-store/lm2j3y4gdxnjotyvhylq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778920/luxury-watch-store/ze0lehizzd0egfht89hx.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778917/luxury-watch-store/whyst0ht5j6uxvrh0fr0.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778916/luxury-watch-store/irqywrsm4o4qrwpnv0ib.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778914/luxury-watch-store/ur6hmuhlrl6go1rnytjy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778913/luxury-watch-store/dq4wmrz0p7sw6whp1nnx.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778912/luxury-watch-store/ybxeho1idgptrzm6onnh.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778910/luxury-watch-store/wxnxevbhnekdgf0ibsnz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778909/luxury-watch-store/rs2t22n548eqwjftu3il.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778901/luxury-watch-store/jjnfzfsnsa1jjx2uqs1q.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778898/luxury-watch-store/puaafbjxutxhp4hihyyd.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778896/luxury-watch-store/ttkrbqgb5grpkvsnj7bq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778895/luxury-watch-store/mzjjhrkgztrroqzknw9r.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778893/luxury-watch-store/mhbg8jmwss1epzn51et8.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778891/luxury-watch-store/rejlzabnqjg15hklsydz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778890/luxury-watch-store/dekv62kkweid8xmoausd.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778889/luxury-watch-store/aidwsszw2rjtpib3j18m.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778886/luxury-watch-store/ydgedalvailgklddasdm.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778884/luxury-watch-store/xe5lcxvqzm1e8tidhgcq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774778883/luxury-watch-store/ugr2enjbyinggmy545uh.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860621/luxury-watch-store/kwi0rohygrlkt8rtatd6.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860620/luxury-watch-store/forgrf66rbmtfezrhlnf.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860618/luxury-watch-store/t9qtcucuy23kny79hhbj.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860617/luxury-watch-store/nvbvrb7efydnr3sxdjrh.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860615/luxury-watch-store/qya7dm8ezg3uh3un9eqc.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860614/luxury-watch-store/w2ky0qmmyp2ue9ldzlzq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860613/luxury-watch-store/c800zxcvtnyj7q7wvhnl.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860611/luxury-watch-store/mrtv5quiacks2xisbqom.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860610/luxury-watch-store/gqg0ahdskhxj17tvbf4p.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860609/luxury-watch-store/kbj387uicy1b4zmq1mzs.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860607/luxury-watch-store/m9nrkfmhauqwibzhx3hr.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860606/luxury-watch-store/upomrk4hcesnibo8ufdu.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860605/luxury-watch-store/uv8mo2s2x1aoznfjisya.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860603/luxury-watch-store/e8zgahxp3kwbednj5xeg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860602/luxury-watch-store/gitf95dgtl9h9qgh6gch.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860601/luxury-watch-store/cc1jnwfflr3tgjti3khz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860600/luxury-watch-store/dqimwah9uu1wgkjyeha9.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860598/luxury-watch-store/yeadziuoq70iaehqyspw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860597/luxury-watch-store/zs4p7bl2whb7f6pbz9lw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860596/luxury-watch-store/dvdde4xoje1iumsprkia.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860595/luxury-watch-store/qsrjwf3xnvgttrnbiyx3.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860594/luxury-watch-store/iekc3ozs9hkksjqkwkit.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860593/luxury-watch-store/n0vuis571arl7hqcgkbh.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860591/luxury-watch-store/fjsfhrkei7z1iwxx2uv4.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860590/luxury-watch-store/mvibvkziuzc87nhnxlxy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860589/luxury-watch-store/x6ehgby2whyayavwkspk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860587/luxury-watch-store/drnivctwdp2rvyek8yxh.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860586/luxury-watch-store/hpyfldzui6zhqz1aprlp.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860584/luxury-watch-store/t9ztw8uris39mvznfcrg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860583/luxury-watch-store/fvgwaubxvosg3vz9zvxx.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860582/luxury-watch-store/hbys4qub2d3akcb9pb7a.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860580/luxury-watch-store/zwdeiqndfrw9afwkb7kb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860579/luxury-watch-store/c1vv5l1gnogt5buel03i.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860578/luxury-watch-store/da1bi8jbhpth2wycqqdh.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860576/luxury-watch-store/lkw2x1ptgg5zqukhpaan.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860575/luxury-watch-store/t6ptlirrolvw7duwryyz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860573/luxury-watch-store/iylb2l6ssmwm9sfwsjs2.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860572/luxury-watch-store/fhndttcd8uthvu4dwkzr.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860571/luxury-watch-store/eq2cc4zdmvp5o3i1lq8q.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860569/luxury-watch-store/crevsswgmvmpioktmbi9.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860568/luxury-watch-store/ouf0ssnzmfch1h8dtijn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860567/luxury-watch-store/swiuyvnb2nkw0riemy4c.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860565/luxury-watch-store/yazjxqjolzatxycz6tgt.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860564/luxury-watch-store/oayzqvufaikxzc0o1f06.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860561/luxury-watch-store/dd5akdpb81r0oxpznmpk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860560/luxury-watch-store/ks8ha4c7t1u0jqvgi18v.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860559/luxury-watch-store/meuznpeivu3nddh1otmi.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860557/luxury-watch-store/f25nuvfhzesektknbcjb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860556/luxury-watch-store/r93pcc4rdy9wf2ihoqm5.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860555/luxury-watch-store/fowhodxadkyjx3lrqd9q.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860554/luxury-watch-store/cevvtknpviez8i8hmaeh.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860553/luxury-watch-store/yvcrginovtyhfxcj1hhk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860551/luxury-watch-store/hqtn8edlqfvflnqwhqza.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860550/luxury-watch-store/ufoyvnxgljzmwtaaonyb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860549/luxury-watch-store/i9utsik3078cexyobo5o.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860547/luxury-watch-store/lkozudfbgdio6kyfr1ux.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860546/luxury-watch-store/iqfcinci74rozyfjahtd.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860545/luxury-watch-store/jk9jbypwzhh4gexyzfx0.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dinrpqxne/image/upload/v1774860407/luxury-watch-store/hgtel11kxs5cu7yotbgj.jpg</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1218,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1079,7 +1226,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1449,12 +1596,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="130.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="130.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1498,7 +1645,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1515,80 +1662,80 @@
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>23</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>24</v>
       </c>
-      <c r="N2" t="s">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>26</v>
       </c>
       <c r="B3">
         <v>87000000</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
       </c>
       <c r="E3">
         <v>36</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>35</v>
       </c>
       <c r="B4">
         <v>1688000000</v>
@@ -1597,42 +1744,42 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>49</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
         <v>37</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
         <v>38</v>
       </c>
-      <c r="H4" t="s">
+      <c r="M4" t="s">
         <v>39</v>
       </c>
-      <c r="I4" t="s">
+      <c r="N4" t="s">
         <v>40</v>
       </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" t="s">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>44</v>
       </c>
       <c r="B5">
         <v>903000000</v>
@@ -1641,1098 +1788,1098 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" t="s">
         <v>46</v>
       </c>
-      <c r="G5" t="s">
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
         <v>47</v>
       </c>
-      <c r="H5" t="s">
+      <c r="N5" t="s">
         <v>48</v>
       </c>
-      <c r="I5" t="s">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>49</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5" t="s">
-        <v>51</v>
-      </c>
-      <c r="N5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>53</v>
       </c>
       <c r="B6">
         <v>9000000</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>30</v>
       </c>
-      <c r="F6" t="s">
-        <v>56</v>
+      <c r="F6" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
         <v>23</v>
       </c>
-      <c r="M6" t="s">
-        <v>24</v>
-      </c>
       <c r="N6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>37000000</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>18</v>
       </c>
-      <c r="F7" t="s">
-        <v>62</v>
+      <c r="F7" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="G7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B8">
         <v>166000000</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <v>8</v>
       </c>
-      <c r="F8" t="s">
-        <v>69</v>
+      <c r="F8" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
         <v>18</v>
       </c>
-      <c r="H8" t="s">
-        <v>19</v>
-      </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" t="s">
         <v>32</v>
       </c>
-      <c r="K8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" t="s">
-        <v>34</v>
-      </c>
       <c r="N8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B9">
         <v>1287000000</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E9">
         <v>21</v>
       </c>
-      <c r="F9" t="s">
-        <v>75</v>
+      <c r="F9" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" t="s">
         <v>38</v>
       </c>
-      <c r="H9" t="s">
+      <c r="M9" t="s">
         <v>39</v>
       </c>
-      <c r="I9" t="s">
-        <v>76</v>
-      </c>
-      <c r="J9" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" t="s">
-        <v>42</v>
-      </c>
       <c r="N9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B10">
         <v>1040000000</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E10">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
-        <v>79</v>
+      <c r="F10" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
         <v>39</v>
       </c>
-      <c r="I10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" t="s">
-        <v>42</v>
-      </c>
       <c r="N10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B11">
         <v>46000000</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E11">
         <v>36</v>
       </c>
-      <c r="F11" t="s">
-        <v>62</v>
+      <c r="F11" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="J11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L11" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B12">
         <v>43000000</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E12">
         <v>25</v>
       </c>
-      <c r="F12" t="s">
-        <v>37</v>
+      <c r="F12" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" t="s">
         <v>47</v>
       </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" t="s">
-        <v>51</v>
-      </c>
       <c r="N12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B13">
         <v>10000000</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E13">
         <v>28</v>
       </c>
-      <c r="F13" t="s">
-        <v>91</v>
+      <c r="F13" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" t="s">
         <v>38</v>
       </c>
-      <c r="H13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" t="s">
-        <v>92</v>
-      </c>
-      <c r="J13" t="s">
-        <v>64</v>
-      </c>
-      <c r="K13" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13" t="s">
-        <v>41</v>
-      </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B14">
         <v>33000000</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E14">
         <v>24</v>
       </c>
-      <c r="F14" t="s">
-        <v>96</v>
+      <c r="F14" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
         <v>32</v>
       </c>
-      <c r="K14" t="s">
-        <v>58</v>
-      </c>
-      <c r="L14" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" t="s">
-        <v>34</v>
-      </c>
       <c r="N14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B15">
         <v>182000000</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E15">
         <v>27</v>
       </c>
-      <c r="F15" t="s">
-        <v>101</v>
+      <c r="F15" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" t="s">
+        <v>90</v>
+      </c>
+      <c r="J15" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L15" t="s">
         <v>38</v>
       </c>
-      <c r="H15" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" t="s">
-        <v>102</v>
-      </c>
-      <c r="J15" t="s">
-        <v>103</v>
-      </c>
-      <c r="K15" t="s">
-        <v>104</v>
-      </c>
-      <c r="L15" t="s">
-        <v>41</v>
-      </c>
       <c r="M15" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B16">
         <v>35000000</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E16">
         <v>30</v>
       </c>
-      <c r="F16" t="s">
-        <v>108</v>
+      <c r="F16" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="J16" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B17">
         <v>127000000</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E17">
         <v>19</v>
       </c>
-      <c r="F17" t="s">
-        <v>62</v>
+      <c r="F17" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" t="s">
+        <v>99</v>
+      </c>
+      <c r="J17" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" t="s">
+        <v>38</v>
+      </c>
+      <c r="M17" t="s">
         <v>47</v>
       </c>
-      <c r="H17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" t="s">
-        <v>112</v>
-      </c>
-      <c r="J17" t="s">
-        <v>64</v>
-      </c>
-      <c r="K17" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17" t="s">
-        <v>41</v>
-      </c>
-      <c r="M17" t="s">
-        <v>51</v>
-      </c>
       <c r="N17" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B18">
         <v>10000000</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E18">
         <v>13</v>
       </c>
-      <c r="F18" t="s">
-        <v>75</v>
+      <c r="F18" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I18" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="J18" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L18" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B19">
         <v>199000000</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E19">
         <v>30</v>
       </c>
-      <c r="F19" t="s">
-        <v>118</v>
+      <c r="F19" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" t="s">
         <v>38</v>
       </c>
-      <c r="H19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" t="s">
-        <v>119</v>
-      </c>
-      <c r="J19" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" t="s">
-        <v>50</v>
-      </c>
-      <c r="L19" t="s">
-        <v>41</v>
-      </c>
       <c r="M19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="B20">
         <v>73000000</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E20">
         <v>13</v>
       </c>
-      <c r="F20" t="s">
-        <v>122</v>
+      <c r="F20" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" t="s">
         <v>38</v>
       </c>
-      <c r="H20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" t="s">
-        <v>123</v>
-      </c>
-      <c r="J20" t="s">
-        <v>64</v>
-      </c>
-      <c r="K20" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" t="s">
-        <v>41</v>
-      </c>
       <c r="M20" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B21">
         <v>212000000</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E21">
         <v>25</v>
       </c>
-      <c r="F21" t="s">
-        <v>127</v>
+      <c r="F21" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="J21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L21" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" t="s">
         <v>32</v>
       </c>
-      <c r="K21" t="s">
-        <v>50</v>
-      </c>
-      <c r="L21" t="s">
-        <v>85</v>
-      </c>
-      <c r="M21" t="s">
-        <v>34</v>
-      </c>
       <c r="N21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B22">
         <v>169000000</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E22">
         <v>49</v>
       </c>
-      <c r="F22" t="s">
-        <v>131</v>
+      <c r="F22" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I22" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="J22" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="B23">
         <v>277000000</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E23">
         <v>17</v>
       </c>
-      <c r="F23" t="s">
-        <v>135</v>
+      <c r="F23" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" t="s">
+        <v>118</v>
+      </c>
+      <c r="J23" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L23" t="s">
         <v>38</v>
       </c>
-      <c r="H23" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" t="s">
-        <v>136</v>
-      </c>
-      <c r="J23" t="s">
-        <v>64</v>
-      </c>
-      <c r="K23" t="s">
-        <v>50</v>
-      </c>
-      <c r="L23" t="s">
-        <v>41</v>
-      </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B24">
         <v>8000000</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G24" t="s">
         <v>17</v>
       </c>
-      <c r="G24" t="s">
-        <v>18</v>
-      </c>
       <c r="H24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="J24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N24" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="B25">
         <v>30000000</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E25">
         <v>33</v>
       </c>
-      <c r="F25" t="s">
-        <v>46</v>
+      <c r="F25" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L25" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M25" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B26">
         <v>169000000</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="E26">
         <v>38</v>
       </c>
-      <c r="F26" t="s">
-        <v>144</v>
+      <c r="F26" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="G26" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="J26" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" t="s">
         <v>21</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>22</v>
       </c>
-      <c r="L26" t="s">
-        <v>23</v>
-      </c>
       <c r="M26" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="B27">
         <v>162000000</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E27">
         <v>19</v>
       </c>
-      <c r="F27" t="s">
-        <v>147</v>
+      <c r="F27" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="G27" t="s">
+        <v>43</v>
+      </c>
+      <c r="H27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" t="s">
+        <v>58</v>
+      </c>
+      <c r="K27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L27" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" t="s">
         <v>47</v>
       </c>
-      <c r="H27" t="s">
-        <v>48</v>
-      </c>
-      <c r="I27" t="s">
-        <v>148</v>
-      </c>
-      <c r="J27" t="s">
-        <v>64</v>
-      </c>
-      <c r="K27" t="s">
-        <v>71</v>
-      </c>
-      <c r="L27" t="s">
-        <v>23</v>
-      </c>
-      <c r="M27" t="s">
-        <v>51</v>
-      </c>
       <c r="N27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B28">
         <v>100000000</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="E28">
         <v>49</v>
       </c>
-      <c r="F28" t="s">
-        <v>151</v>
+      <c r="F28" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="G28" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I28" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="J28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B29">
         <v>146000000</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E29">
         <v>13</v>
       </c>
-      <c r="F29" t="s">
-        <v>154</v>
+      <c r="F29" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="G29" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I29" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="J29" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L29" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M29" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N29" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="B30">
         <v>1882000000</v>
@@ -2746,301 +2893,301 @@
       <c r="E30">
         <v>30</v>
       </c>
-      <c r="F30" t="s">
-        <v>108</v>
+      <c r="F30" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="G30" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="J30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K30" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L30" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M30" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N30" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="B31">
         <v>189000000</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="E31">
         <v>33</v>
       </c>
-      <c r="F31" t="s">
-        <v>144</v>
+      <c r="F31" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" t="s">
+        <v>138</v>
+      </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" t="s">
+        <v>38</v>
+      </c>
+      <c r="M31" t="s">
         <v>39</v>
       </c>
-      <c r="I31" t="s">
-        <v>160</v>
-      </c>
-      <c r="J31" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" t="s">
-        <v>50</v>
-      </c>
-      <c r="L31" t="s">
-        <v>41</v>
-      </c>
-      <c r="M31" t="s">
-        <v>42</v>
-      </c>
       <c r="N31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="B32">
         <v>442000000</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="E32">
         <v>46</v>
       </c>
-      <c r="F32" t="s">
-        <v>162</v>
+      <c r="F32" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="G32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="J32" t="s">
+        <v>58</v>
+      </c>
+      <c r="K32" t="s">
         <v>64</v>
       </c>
-      <c r="K32" t="s">
-        <v>71</v>
-      </c>
       <c r="L32" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M32" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N32" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="B33">
         <v>517000000</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="E33">
         <v>9</v>
       </c>
-      <c r="F33" t="s">
-        <v>135</v>
+      <c r="F33" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="G33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I33" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="J33" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L33" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M33" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N33" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="B34">
         <v>711000000</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E34">
         <v>11</v>
       </c>
-      <c r="F34" t="s">
-        <v>169</v>
+      <c r="F34" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" t="s">
+        <v>146</v>
+      </c>
+      <c r="J34" t="s">
+        <v>58</v>
+      </c>
+      <c r="K34" t="s">
+        <v>92</v>
+      </c>
+      <c r="L34" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" t="s">
         <v>39</v>
       </c>
-      <c r="I34" t="s">
-        <v>170</v>
-      </c>
-      <c r="J34" t="s">
-        <v>64</v>
-      </c>
-      <c r="K34" t="s">
-        <v>104</v>
-      </c>
-      <c r="L34" t="s">
-        <v>23</v>
-      </c>
-      <c r="M34" t="s">
-        <v>42</v>
-      </c>
       <c r="N34" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B35">
         <v>1295000000</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="E35">
         <v>29</v>
       </c>
-      <c r="F35" t="s">
-        <v>122</v>
+      <c r="F35" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="G35" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H35" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" t="s">
+        <v>149</v>
+      </c>
+      <c r="J35" t="s">
         <v>30</v>
       </c>
-      <c r="I35" t="s">
-        <v>173</v>
-      </c>
-      <c r="J35" t="s">
-        <v>32</v>
-      </c>
       <c r="K35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M35" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N35" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="B36">
         <v>2415000000</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="E36">
         <v>20</v>
       </c>
-      <c r="F36" t="s">
-        <v>175</v>
+      <c r="F36" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="G36" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H36" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" t="s">
+        <v>151</v>
+      </c>
+      <c r="J36" t="s">
         <v>30</v>
       </c>
-      <c r="I36" t="s">
-        <v>176</v>
-      </c>
-      <c r="J36" t="s">
-        <v>32</v>
-      </c>
       <c r="K36" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L36" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="B37">
         <v>1392000000</v>
@@ -3054,917 +3201,917 @@
       <c r="E37">
         <v>34</v>
       </c>
-      <c r="F37" t="s">
-        <v>178</v>
+      <c r="F37" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="G37" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H37" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I37" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="J37" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" t="s">
         <v>21</v>
       </c>
-      <c r="K37" t="s">
-        <v>22</v>
-      </c>
       <c r="L37" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M37" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="B38">
         <v>39000000</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E38">
         <v>47</v>
       </c>
-      <c r="F38" t="s">
-        <v>181</v>
+      <c r="F38" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="G38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I38" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="J38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K38" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L38" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M38" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N38" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="B39">
         <v>47000000</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D39" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="E39">
         <v>20</v>
       </c>
-      <c r="F39" t="s">
-        <v>185</v>
+      <c r="F39" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="G39" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" t="s">
+        <v>158</v>
+      </c>
+      <c r="J39" t="s">
+        <v>58</v>
+      </c>
+      <c r="K39" t="s">
+        <v>92</v>
+      </c>
+      <c r="L39" t="s">
+        <v>76</v>
+      </c>
+      <c r="M39" t="s">
         <v>39</v>
       </c>
-      <c r="I39" t="s">
-        <v>186</v>
-      </c>
-      <c r="J39" t="s">
-        <v>64</v>
-      </c>
-      <c r="K39" t="s">
-        <v>104</v>
-      </c>
-      <c r="L39" t="s">
-        <v>85</v>
-      </c>
-      <c r="M39" t="s">
-        <v>42</v>
-      </c>
       <c r="N39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="B40">
         <v>31000000</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E40">
         <v>36</v>
       </c>
-      <c r="F40" t="s">
-        <v>189</v>
+      <c r="F40" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="G40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" t="s">
+        <v>161</v>
+      </c>
+      <c r="J40" t="s">
+        <v>58</v>
+      </c>
+      <c r="K40" t="s">
+        <v>64</v>
+      </c>
+      <c r="L40" t="s">
+        <v>59</v>
+      </c>
+      <c r="M40" t="s">
         <v>39</v>
       </c>
-      <c r="I40" t="s">
-        <v>190</v>
-      </c>
-      <c r="J40" t="s">
-        <v>64</v>
-      </c>
-      <c r="K40" t="s">
-        <v>71</v>
-      </c>
-      <c r="L40" t="s">
-        <v>65</v>
-      </c>
-      <c r="M40" t="s">
-        <v>42</v>
-      </c>
       <c r="N40" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="B41">
         <v>9000000</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D41" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E41">
         <v>27</v>
       </c>
-      <c r="F41" t="s">
-        <v>29</v>
+      <c r="F41" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="G41" t="s">
+        <v>35</v>
+      </c>
+      <c r="H41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I41" t="s">
+        <v>163</v>
+      </c>
+      <c r="J41" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" t="s">
+        <v>31</v>
+      </c>
+      <c r="L41" t="s">
         <v>38</v>
       </c>
-      <c r="H41" t="s">
-        <v>48</v>
-      </c>
-      <c r="I41" t="s">
-        <v>192</v>
-      </c>
-      <c r="J41" t="s">
-        <v>21</v>
-      </c>
-      <c r="K41" t="s">
-        <v>33</v>
-      </c>
-      <c r="L41" t="s">
-        <v>41</v>
-      </c>
       <c r="M41" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N41" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="B42">
         <v>428000000</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="E42">
         <v>46</v>
       </c>
-      <c r="F42" t="s">
-        <v>144</v>
+      <c r="F42" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="G42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I42" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="J42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K42" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L42" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M42" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="B43">
         <v>343000000</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E43">
         <v>42</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G43" t="s">
         <v>17</v>
       </c>
-      <c r="G43" t="s">
-        <v>18</v>
-      </c>
       <c r="H43" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I43" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="J43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K43" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M43" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N43" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="B44">
         <v>11000000</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="E44">
         <v>17</v>
       </c>
-      <c r="F44" t="s">
-        <v>200</v>
+      <c r="F44" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="G44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H44" t="s">
+        <v>44</v>
+      </c>
+      <c r="I44" t="s">
+        <v>171</v>
+      </c>
+      <c r="J44" t="s">
+        <v>91</v>
+      </c>
+      <c r="K44" t="s">
+        <v>92</v>
+      </c>
+      <c r="L44" t="s">
         <v>38</v>
       </c>
-      <c r="H44" t="s">
+      <c r="M44" t="s">
+        <v>23</v>
+      </c>
+      <c r="N44" t="s">
         <v>48</v>
       </c>
-      <c r="I44" t="s">
-        <v>201</v>
-      </c>
-      <c r="J44" t="s">
-        <v>103</v>
-      </c>
-      <c r="K44" t="s">
-        <v>104</v>
-      </c>
-      <c r="L44" t="s">
-        <v>41</v>
-      </c>
-      <c r="M44" t="s">
-        <v>24</v>
-      </c>
-      <c r="N44" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="B45">
         <v>44000000</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D45" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E45">
         <v>42</v>
       </c>
-      <c r="F45" t="s">
-        <v>203</v>
+      <c r="F45" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="G45" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="J45" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K45" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L45" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N45" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="B46">
         <v>547000000</v>
       </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="E46">
         <v>49</v>
       </c>
-      <c r="F46" t="s">
-        <v>127</v>
+      <c r="F46" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="G46" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" t="s">
+        <v>176</v>
+      </c>
+      <c r="J46" t="s">
+        <v>58</v>
+      </c>
+      <c r="K46" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" t="s">
         <v>47</v>
       </c>
-      <c r="H46" t="s">
-        <v>19</v>
-      </c>
-      <c r="I46" t="s">
-        <v>207</v>
-      </c>
-      <c r="J46" t="s">
-        <v>64</v>
-      </c>
-      <c r="K46" t="s">
-        <v>22</v>
-      </c>
-      <c r="L46" t="s">
-        <v>23</v>
-      </c>
-      <c r="M46" t="s">
-        <v>51</v>
-      </c>
       <c r="N46" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="B47">
         <v>472000000</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E47">
         <v>18</v>
       </c>
-      <c r="F47" t="s">
-        <v>209</v>
+      <c r="F47" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="G47" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" t="s">
         <v>18</v>
       </c>
-      <c r="H47" t="s">
-        <v>19</v>
-      </c>
       <c r="I47" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="J47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L47" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N47" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="B48">
         <v>13000000</v>
       </c>
       <c r="C48" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="E48">
         <v>30</v>
       </c>
-      <c r="F48" t="s">
-        <v>212</v>
+      <c r="F48" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="G48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" t="s">
+        <v>180</v>
+      </c>
+      <c r="J48" t="s">
+        <v>30</v>
+      </c>
+      <c r="K48" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" t="s">
+        <v>59</v>
+      </c>
+      <c r="M48" t="s">
         <v>47</v>
       </c>
-      <c r="H48" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48" t="s">
-        <v>213</v>
-      </c>
-      <c r="J48" t="s">
-        <v>32</v>
-      </c>
-      <c r="K48" t="s">
-        <v>58</v>
-      </c>
-      <c r="L48" t="s">
-        <v>65</v>
-      </c>
-      <c r="M48" t="s">
-        <v>51</v>
-      </c>
       <c r="N48" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="B49">
         <v>898000000</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="E49">
         <v>25</v>
       </c>
-      <c r="F49" t="s">
-        <v>209</v>
+      <c r="F49" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="G49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" t="s">
+        <v>183</v>
+      </c>
+      <c r="J49" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49" t="s">
+        <v>53</v>
+      </c>
+      <c r="L49" t="s">
         <v>38</v>
       </c>
-      <c r="H49" t="s">
-        <v>39</v>
-      </c>
-      <c r="I49" t="s">
-        <v>216</v>
-      </c>
-      <c r="J49" t="s">
-        <v>32</v>
-      </c>
-      <c r="K49" t="s">
-        <v>58</v>
-      </c>
-      <c r="L49" t="s">
-        <v>41</v>
-      </c>
       <c r="M49" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N49" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="B50">
         <v>12000000</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="E50">
         <v>20</v>
       </c>
-      <c r="F50" t="s">
-        <v>62</v>
+      <c r="F50" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="G50" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I50" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="J50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L50" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M50" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N50" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="B51">
         <v>460000000</v>
       </c>
       <c r="C51" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D51" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="E51">
         <v>26</v>
       </c>
-      <c r="F51" t="s">
-        <v>162</v>
+      <c r="F51" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="G51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I51" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="J51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L51" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M51" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N51" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="B52">
         <v>466000000</v>
       </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D52" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E52">
         <v>28</v>
       </c>
-      <c r="F52" t="s">
-        <v>162</v>
+      <c r="F52" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="G52" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="J52" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K52" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L52" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M52" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="B53">
         <v>790000000</v>
       </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D53" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E53">
         <v>50</v>
       </c>
-      <c r="F53" t="s">
-        <v>224</v>
+      <c r="F53" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="G53" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" t="s">
         <v>18</v>
       </c>
-      <c r="H53" t="s">
-        <v>19</v>
-      </c>
       <c r="I53" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="J53" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L53" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M53" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N53" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="B54">
         <v>10000000</v>
       </c>
       <c r="C54" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D54" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="E54">
         <v>9</v>
       </c>
-      <c r="F54" t="s">
-        <v>175</v>
+      <c r="F54" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="G54" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="J54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L54" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M54" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N54" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="B55">
         <v>87000000</v>
       </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="E55">
         <v>40</v>
       </c>
-      <c r="F55" t="s">
-        <v>29</v>
+      <c r="F55" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H55" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="J55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K55" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" t="s">
         <v>22</v>
       </c>
-      <c r="L55" t="s">
-        <v>23</v>
-      </c>
       <c r="M55" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N55" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="B56">
         <v>152000000</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E56">
         <v>20</v>
       </c>
-      <c r="F56" t="s">
-        <v>232</v>
+      <c r="F56" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="G56" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H56" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I56" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="J56" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K56" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M56" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N56" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="B57">
         <v>114000000</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E57">
         <v>42</v>
       </c>
-      <c r="F57" t="s">
-        <v>203</v>
+      <c r="F57" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="G57" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H57" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I57" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="J57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M57" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N57" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="B58">
         <v>1257000000</v>
@@ -3978,37 +4125,37 @@
       <c r="E58">
         <v>30</v>
       </c>
-      <c r="F58" t="s">
-        <v>237</v>
+      <c r="F58" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="G58" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I58" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="J58" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L58" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M58" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N58" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="B59">
         <v>2802000000</v>
@@ -4017,262 +4164,262 @@
         <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="E59">
         <v>10</v>
       </c>
-      <c r="F59" t="s">
-        <v>154</v>
+      <c r="F59" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="G59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I59" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="J59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K59" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M59" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N59" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="B60">
         <v>371000000</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D60" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="E60">
         <v>23</v>
       </c>
-      <c r="F60" t="s">
-        <v>69</v>
+      <c r="F60" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="G60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I60" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="J60" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L60" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M60" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N60" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="B61">
         <v>18000000</v>
       </c>
       <c r="C61" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="E61">
         <v>5</v>
       </c>
-      <c r="F61" t="s">
-        <v>245</v>
+      <c r="F61" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="G61" t="s">
+        <v>43</v>
+      </c>
+      <c r="H61" t="s">
+        <v>36</v>
+      </c>
+      <c r="I61" t="s">
+        <v>209</v>
+      </c>
+      <c r="J61" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61" t="s">
+        <v>64</v>
+      </c>
+      <c r="L61" t="s">
+        <v>22</v>
+      </c>
+      <c r="M61" t="s">
         <v>47</v>
       </c>
-      <c r="H61" t="s">
-        <v>39</v>
-      </c>
-      <c r="I61" t="s">
-        <v>246</v>
-      </c>
-      <c r="J61" t="s">
-        <v>32</v>
-      </c>
-      <c r="K61" t="s">
-        <v>71</v>
-      </c>
-      <c r="L61" t="s">
-        <v>23</v>
-      </c>
-      <c r="M61" t="s">
-        <v>51</v>
-      </c>
       <c r="N61" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="B62">
         <v>437000000</v>
       </c>
       <c r="C62" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="E62">
         <v>5</v>
       </c>
-      <c r="F62" t="s">
-        <v>69</v>
+      <c r="F62" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="G62" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62" t="s">
         <v>18</v>
       </c>
-      <c r="H62" t="s">
-        <v>19</v>
-      </c>
       <c r="I62" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="J62" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K62" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L62" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M62" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N62" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="B63">
         <v>1229000000</v>
       </c>
       <c r="C63" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D63" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E63">
         <v>8</v>
       </c>
-      <c r="F63" t="s">
-        <v>245</v>
+      <c r="F63" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="G63" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" t="s">
         <v>18</v>
       </c>
-      <c r="H63" t="s">
-        <v>19</v>
-      </c>
       <c r="I63" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="J63" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M63" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N63" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="B64">
         <v>12000000</v>
       </c>
       <c r="C64" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D64" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="E64">
         <v>22</v>
       </c>
-      <c r="F64" t="s">
-        <v>203</v>
+      <c r="F64" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="G64" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H64" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I64" t="s">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="J64" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L64" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N64" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="B65">
         <v>1254000000</v>
@@ -4281,86 +4428,86 @@
         <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="E65">
         <v>37</v>
       </c>
-      <c r="F65" t="s">
-        <v>135</v>
+      <c r="F65" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="G65" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H65" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I65" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
       <c r="J65" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L65" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M65" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N65" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="B66">
         <v>66000000</v>
       </c>
       <c r="C66" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D66" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="E66">
         <v>34</v>
       </c>
-      <c r="F66" t="s">
-        <v>259</v>
+      <c r="F66" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="G66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="J66" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L66" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M66" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N66" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="B67">
         <v>1544000000</v>
@@ -4369,1450 +4516,1450 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="E67">
         <v>12</v>
       </c>
-      <c r="F67" t="s">
-        <v>56</v>
+      <c r="F67" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="G67" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I67" t="s">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="J67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K67" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L67" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M67" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N67" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="B68">
         <v>180000000</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E68">
         <v>48</v>
       </c>
-      <c r="F68" t="s">
-        <v>175</v>
+      <c r="F68" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I68" t="s">
-        <v>264</v>
+        <v>226</v>
       </c>
       <c r="J68" t="s">
+        <v>30</v>
+      </c>
+      <c r="K68" t="s">
+        <v>64</v>
+      </c>
+      <c r="L68" t="s">
+        <v>76</v>
+      </c>
+      <c r="M68" t="s">
         <v>32</v>
       </c>
-      <c r="K68" t="s">
-        <v>71</v>
-      </c>
-      <c r="L68" t="s">
-        <v>85</v>
-      </c>
-      <c r="M68" t="s">
-        <v>34</v>
-      </c>
       <c r="N68" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="B69">
         <v>977000000</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D69" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="E69">
         <v>7</v>
       </c>
-      <c r="F69" t="s">
-        <v>46</v>
+      <c r="F69" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="G69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" t="s">
+        <v>228</v>
+      </c>
+      <c r="J69" t="s">
+        <v>91</v>
+      </c>
+      <c r="K69" t="s">
+        <v>53</v>
+      </c>
+      <c r="L69" t="s">
         <v>38</v>
       </c>
-      <c r="H69" t="s">
-        <v>30</v>
-      </c>
-      <c r="I69" t="s">
-        <v>266</v>
-      </c>
-      <c r="J69" t="s">
-        <v>103</v>
-      </c>
-      <c r="K69" t="s">
-        <v>58</v>
-      </c>
-      <c r="L69" t="s">
-        <v>41</v>
-      </c>
       <c r="M69" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N69" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>267</v>
+        <v>229</v>
       </c>
       <c r="B70">
         <v>18000000</v>
       </c>
       <c r="C70" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E70">
         <v>48</v>
       </c>
-      <c r="F70" t="s">
-        <v>147</v>
+      <c r="F70" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="G70" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H70" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I70" t="s">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="J70" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L70" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="B71">
         <v>168000000</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E71">
         <v>28</v>
       </c>
-      <c r="F71" t="s">
-        <v>127</v>
+      <c r="F71" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="G71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I71" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="J71" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L71" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M71" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N71" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="B72">
         <v>23000000</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D72" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E72">
         <v>16</v>
       </c>
-      <c r="F72" t="s">
-        <v>189</v>
+      <c r="F72" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="G72" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>272</v>
+        <v>234</v>
       </c>
       <c r="J72" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L72" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M72" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N72" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="B73">
         <v>11000000</v>
       </c>
       <c r="C73" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D73" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="E73">
         <v>46</v>
       </c>
-      <c r="F73" t="s">
-        <v>275</v>
+      <c r="F73" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="G73" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="J73" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K73" t="s">
+        <v>21</v>
+      </c>
+      <c r="L73" t="s">
         <v>22</v>
       </c>
-      <c r="L73" t="s">
-        <v>23</v>
-      </c>
       <c r="M73" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N73" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="B74">
         <v>24000000</v>
       </c>
       <c r="C74" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D74" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E74">
         <v>29</v>
       </c>
-      <c r="F74" t="s">
-        <v>162</v>
+      <c r="F74" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="G74" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H74" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I74" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="J74" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K74" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L74" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M74" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N74" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="B75">
         <v>93000000</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D75" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="E75">
         <v>30</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G75" t="s">
         <v>17</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>18</v>
       </c>
-      <c r="H75" t="s">
-        <v>19</v>
-      </c>
       <c r="I75" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="J75" t="s">
+        <v>30</v>
+      </c>
+      <c r="K75" t="s">
+        <v>46</v>
+      </c>
+      <c r="L75" t="s">
+        <v>59</v>
+      </c>
+      <c r="M75" t="s">
         <v>32</v>
       </c>
-      <c r="K75" t="s">
-        <v>50</v>
-      </c>
-      <c r="L75" t="s">
-        <v>65</v>
-      </c>
-      <c r="M75" t="s">
-        <v>34</v>
-      </c>
       <c r="N75" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="B76">
         <v>426000000</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D76" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E76">
         <v>39</v>
       </c>
-      <c r="F76" t="s">
-        <v>283</v>
+      <c r="F76" s="1" t="s">
+        <v>371</v>
       </c>
       <c r="G76" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H76" t="s">
+        <v>28</v>
+      </c>
+      <c r="I76" t="s">
+        <v>244</v>
+      </c>
+      <c r="J76" t="s">
         <v>30</v>
       </c>
-      <c r="I76" t="s">
-        <v>284</v>
-      </c>
-      <c r="J76" t="s">
-        <v>32</v>
-      </c>
       <c r="K76" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L76" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M76" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N76" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>285</v>
+        <v>245</v>
       </c>
       <c r="B77">
         <v>74000000</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E77">
         <v>20</v>
       </c>
-      <c r="F77" t="s">
-        <v>108</v>
+      <c r="F77" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="G77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H77" t="s">
+        <v>36</v>
+      </c>
+      <c r="I77" t="s">
+        <v>246</v>
+      </c>
+      <c r="J77" t="s">
+        <v>30</v>
+      </c>
+      <c r="K77" t="s">
+        <v>31</v>
+      </c>
+      <c r="L77" t="s">
+        <v>38</v>
+      </c>
+      <c r="M77" t="s">
         <v>39</v>
       </c>
-      <c r="I77" t="s">
-        <v>286</v>
-      </c>
-      <c r="J77" t="s">
-        <v>32</v>
-      </c>
-      <c r="K77" t="s">
-        <v>33</v>
-      </c>
-      <c r="L77" t="s">
-        <v>41</v>
-      </c>
-      <c r="M77" t="s">
-        <v>42</v>
-      </c>
       <c r="N77" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>287</v>
+        <v>247</v>
       </c>
       <c r="B78">
         <v>598000000</v>
       </c>
       <c r="C78" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="E78">
         <v>19</v>
       </c>
-      <c r="F78" t="s">
-        <v>212</v>
+      <c r="F78" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="G78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I78" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="J78" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L78" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M78" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N78" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="B79">
         <v>1758000000</v>
       </c>
       <c r="C79" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="E79">
         <v>6</v>
       </c>
-      <c r="F79" t="s">
-        <v>135</v>
+      <c r="F79" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="G79" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="J79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K79" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L79" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N79" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="B80">
         <v>85000000</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D80" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="E80">
         <v>49</v>
       </c>
-      <c r="F80" t="s">
-        <v>259</v>
+      <c r="F80" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="G80" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H80" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I80" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="J80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80" t="s">
+        <v>53</v>
+      </c>
+      <c r="L80" t="s">
+        <v>59</v>
+      </c>
+      <c r="M80" t="s">
         <v>32</v>
       </c>
-      <c r="K80" t="s">
-        <v>58</v>
-      </c>
-      <c r="L80" t="s">
-        <v>65</v>
-      </c>
-      <c r="M80" t="s">
-        <v>34</v>
-      </c>
       <c r="N80" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="B81">
         <v>439000000</v>
       </c>
       <c r="C81" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D81" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E81">
         <v>7</v>
       </c>
-      <c r="F81" t="s">
-        <v>294</v>
+      <c r="F81" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="G81" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H81" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
       <c r="J81" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L81" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M81" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N81" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="B82">
         <v>2102000000</v>
       </c>
       <c r="C82" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D82" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E82">
         <v>4</v>
       </c>
-      <c r="F82" t="s">
-        <v>297</v>
+      <c r="F82" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="G82" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="J82" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L82" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M82" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N82" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="B83">
         <v>34000000</v>
       </c>
       <c r="C83" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D83" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="E83">
         <v>2</v>
       </c>
-      <c r="F83" t="s">
-        <v>131</v>
+      <c r="F83" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="G83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I83" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="J83" t="s">
+        <v>58</v>
+      </c>
+      <c r="K83" t="s">
         <v>64</v>
       </c>
-      <c r="K83" t="s">
-        <v>71</v>
-      </c>
       <c r="L83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M83" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N83" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="B84">
         <v>273000000</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D84" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E84">
         <v>29</v>
       </c>
-      <c r="F84" t="s">
-        <v>37</v>
+      <c r="F84" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="G84" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H84" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" t="s">
+        <v>260</v>
+      </c>
+      <c r="J84" t="s">
         <v>30</v>
       </c>
-      <c r="I84" t="s">
-        <v>302</v>
-      </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
+        <v>46</v>
+      </c>
+      <c r="L84" t="s">
+        <v>59</v>
+      </c>
+      <c r="M84" t="s">
         <v>32</v>
       </c>
-      <c r="K84" t="s">
-        <v>50</v>
-      </c>
-      <c r="L84" t="s">
-        <v>65</v>
-      </c>
-      <c r="M84" t="s">
-        <v>34</v>
-      </c>
       <c r="N84" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="B85">
         <v>147000000</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D85" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="E85">
         <v>9</v>
       </c>
-      <c r="F85" t="s">
-        <v>209</v>
+      <c r="F85" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="G85" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H85" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I85" t="s">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="J85" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K85" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M85" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N85" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="B86">
         <v>17000000</v>
       </c>
       <c r="C86" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D86" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="E86">
         <v>27</v>
       </c>
-      <c r="F86" t="s">
-        <v>189</v>
+      <c r="F86" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="G86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I86" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="J86" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K86" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L86" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M86" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N86" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="B87">
         <v>18000000</v>
       </c>
       <c r="C87" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D87" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="E87">
         <v>44</v>
       </c>
-      <c r="F87" t="s">
-        <v>135</v>
+      <c r="F87" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="G87" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H87" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I87" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="J87" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L87" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M87" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N87" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="B88">
         <v>18000000</v>
       </c>
       <c r="C88" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D88" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="E88">
         <v>33</v>
       </c>
-      <c r="F88" t="s">
-        <v>131</v>
+      <c r="F88" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="G88" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H88" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I88" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="J88" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K88" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M88" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N88" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="B89">
         <v>897000000</v>
       </c>
       <c r="C89" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D89" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E89">
         <v>16</v>
       </c>
-      <c r="F89" t="s">
-        <v>181</v>
+      <c r="F89" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="G89" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H89" t="s">
+        <v>44</v>
+      </c>
+      <c r="I89" t="s">
+        <v>273</v>
+      </c>
+      <c r="J89" t="s">
+        <v>58</v>
+      </c>
+      <c r="K89" t="s">
+        <v>31</v>
+      </c>
+      <c r="L89" t="s">
+        <v>76</v>
+      </c>
+      <c r="M89" t="s">
+        <v>93</v>
+      </c>
+      <c r="N89" t="s">
         <v>48</v>
       </c>
-      <c r="I89" t="s">
-        <v>315</v>
-      </c>
-      <c r="J89" t="s">
-        <v>64</v>
-      </c>
-      <c r="K89" t="s">
-        <v>33</v>
-      </c>
-      <c r="L89" t="s">
-        <v>85</v>
-      </c>
-      <c r="M89" t="s">
-        <v>105</v>
-      </c>
-      <c r="N89" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="B90">
         <v>992000000</v>
       </c>
       <c r="C90" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D90" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="E90">
         <v>48</v>
       </c>
-      <c r="F90" t="s">
-        <v>122</v>
+      <c r="F90" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="G90" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" t="s">
         <v>18</v>
       </c>
-      <c r="H90" t="s">
-        <v>19</v>
-      </c>
       <c r="I90" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="J90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K90" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L90" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M90" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N90" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="B91">
         <v>339000000</v>
       </c>
       <c r="C91" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D91" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E91">
         <v>45</v>
       </c>
-      <c r="F91" t="s">
-        <v>154</v>
+      <c r="F91" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="G91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H91" t="s">
+        <v>36</v>
+      </c>
+      <c r="I91" t="s">
+        <v>279</v>
+      </c>
+      <c r="J91" t="s">
+        <v>91</v>
+      </c>
+      <c r="K91" t="s">
+        <v>64</v>
+      </c>
+      <c r="L91" t="s">
+        <v>38</v>
+      </c>
+      <c r="M91" t="s">
         <v>39</v>
       </c>
-      <c r="I91" t="s">
-        <v>321</v>
-      </c>
-      <c r="J91" t="s">
-        <v>103</v>
-      </c>
-      <c r="K91" t="s">
-        <v>71</v>
-      </c>
-      <c r="L91" t="s">
-        <v>41</v>
-      </c>
-      <c r="M91" t="s">
-        <v>42</v>
-      </c>
       <c r="N91" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="B92">
         <v>115000000</v>
       </c>
       <c r="C92" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E92">
         <v>44</v>
       </c>
-      <c r="F92" t="s">
-        <v>46</v>
+      <c r="F92" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="G92" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="J92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K92" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L92" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M92" t="s">
+        <v>23</v>
+      </c>
+      <c r="N92" t="s">
         <v>24</v>
       </c>
-      <c r="N92" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>324</v>
+        <v>282</v>
       </c>
       <c r="B93">
         <v>1882000000</v>
       </c>
       <c r="C93" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D93" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E93">
         <v>10</v>
       </c>
-      <c r="F93" t="s">
-        <v>209</v>
+      <c r="F93" s="1" t="s">
+        <v>387</v>
       </c>
       <c r="G93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I93" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="J93" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K93" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L93" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M93" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N93" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="B94">
         <v>1476000000</v>
       </c>
       <c r="C94" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D94" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E94">
         <v>40</v>
       </c>
-      <c r="F94" t="s">
-        <v>327</v>
+      <c r="F94" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="G94" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H94" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I94" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="J94" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K94" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L94" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M94" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N94" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="B95">
         <v>18000000</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D95" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="E95">
         <v>34</v>
       </c>
-      <c r="F95" t="s">
-        <v>178</v>
+      <c r="F95" s="1" t="s">
+        <v>389</v>
       </c>
       <c r="G95" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H95" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I95" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
       <c r="J95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K95" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L95" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M95" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N95" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="B96">
         <v>474000000</v>
       </c>
       <c r="C96" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="E96">
         <v>41</v>
       </c>
-      <c r="F96" t="s">
-        <v>46</v>
+      <c r="F96" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="G96" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H96" t="s">
+        <v>36</v>
+      </c>
+      <c r="I96" t="s">
+        <v>290</v>
+      </c>
+      <c r="J96" t="s">
+        <v>20</v>
+      </c>
+      <c r="K96" t="s">
+        <v>92</v>
+      </c>
+      <c r="L96" t="s">
+        <v>59</v>
+      </c>
+      <c r="M96" t="s">
         <v>39</v>
       </c>
-      <c r="I96" t="s">
-        <v>333</v>
-      </c>
-      <c r="J96" t="s">
-        <v>21</v>
-      </c>
-      <c r="K96" t="s">
-        <v>104</v>
-      </c>
-      <c r="L96" t="s">
-        <v>65</v>
-      </c>
-      <c r="M96" t="s">
-        <v>42</v>
-      </c>
       <c r="N96" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="B97">
         <v>113000000</v>
       </c>
       <c r="C97" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="E97">
         <v>44</v>
       </c>
-      <c r="F97" t="s">
-        <v>335</v>
+      <c r="F97" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="G97" t="s">
+        <v>35</v>
+      </c>
+      <c r="H97" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s">
+        <v>292</v>
+      </c>
+      <c r="J97" t="s">
+        <v>58</v>
+      </c>
+      <c r="K97" t="s">
+        <v>46</v>
+      </c>
+      <c r="L97" t="s">
         <v>38</v>
       </c>
-      <c r="H97" t="s">
-        <v>19</v>
-      </c>
-      <c r="I97" t="s">
-        <v>336</v>
-      </c>
-      <c r="J97" t="s">
-        <v>64</v>
-      </c>
-      <c r="K97" t="s">
-        <v>50</v>
-      </c>
-      <c r="L97" t="s">
-        <v>41</v>
-      </c>
       <c r="M97" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N97" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="B98">
         <v>42000000</v>
       </c>
       <c r="C98" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D98" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="E98">
         <v>46</v>
       </c>
-      <c r="F98" t="s">
-        <v>245</v>
+      <c r="F98" s="1" t="s">
+        <v>392</v>
       </c>
       <c r="G98" t="s">
+        <v>43</v>
+      </c>
+      <c r="H98" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s">
+        <v>294</v>
+      </c>
+      <c r="J98" t="s">
+        <v>58</v>
+      </c>
+      <c r="K98" t="s">
+        <v>64</v>
+      </c>
+      <c r="L98" t="s">
+        <v>76</v>
+      </c>
+      <c r="M98" t="s">
         <v>47</v>
       </c>
-      <c r="H98" t="s">
-        <v>19</v>
-      </c>
-      <c r="I98" t="s">
-        <v>338</v>
-      </c>
-      <c r="J98" t="s">
-        <v>64</v>
-      </c>
-      <c r="K98" t="s">
-        <v>71</v>
-      </c>
-      <c r="L98" t="s">
-        <v>85</v>
-      </c>
-      <c r="M98" t="s">
-        <v>51</v>
-      </c>
       <c r="N98" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="B99">
         <v>138000000</v>
       </c>
       <c r="C99" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D99" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E99">
         <v>50</v>
       </c>
-      <c r="F99" t="s">
-        <v>96</v>
+      <c r="F99" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="G99" t="s">
+        <v>17</v>
+      </c>
+      <c r="H99" t="s">
         <v>18</v>
       </c>
-      <c r="H99" t="s">
-        <v>19</v>
-      </c>
       <c r="I99" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="J99" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K99" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L99" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M99" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N99" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>341</v>
+        <v>297</v>
       </c>
       <c r="B100">
         <v>2388000000</v>
@@ -5826,85 +5973,184 @@
       <c r="E100">
         <v>30</v>
       </c>
-      <c r="F100" t="s">
-        <v>69</v>
+      <c r="F100" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="G100" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H100" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I100" t="s">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="J100" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K100" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M100" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N100" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="B101">
         <v>741000000</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D101" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="E101">
         <v>35</v>
       </c>
-      <c r="F101" t="s">
-        <v>62</v>
+      <c r="F101" s="1" t="s">
+        <v>395</v>
       </c>
       <c r="G101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H101" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I101" t="s">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="J101" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K101" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L101" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N101" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{63C7249A-0617-49C9-BB50-BBB1B635C283}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{31F54567-2C88-41F0-B86D-3640EF13ED2A}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{09D63418-9BE1-4EA8-99C0-2B18B00D246E}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{09C38775-C58C-419E-94F2-3301B6750FD9}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{3EDDE523-9EF0-4DDD-9EC2-BC78D460EAB8}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{68EC741C-F36E-4E82-BBC2-B18D4DE86276}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{F0318BEF-7DBA-460D-9D2F-320B4EE0EC31}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{322071B1-C3E3-4CFA-BC6B-1F828851454D}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{F86101BC-CAEB-4663-9A0F-CA4ED71FB1E3}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{99B4045D-F936-454C-8776-BEADFF0BB539}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{505B62E2-B702-49F7-A60F-C6D1E871EACC}"/>
+    <hyperlink ref="F13" r:id="rId12" xr:uid="{849B5AED-9E29-4E5C-A256-DB80DCD6B612}"/>
+    <hyperlink ref="F14" r:id="rId13" xr:uid="{1A41609A-63F0-456E-98EB-08AFA559975C}"/>
+    <hyperlink ref="F15" r:id="rId14" xr:uid="{F16F39E7-C17B-40AC-9B64-96BA9C71D041}"/>
+    <hyperlink ref="F16" r:id="rId15" xr:uid="{B6723FA2-9EE1-48FE-A74F-20EF710C3844}"/>
+    <hyperlink ref="F17" r:id="rId16" xr:uid="{6846E637-AB87-412E-8ACA-DCCEBB54CC34}"/>
+    <hyperlink ref="F18" r:id="rId17" xr:uid="{C841E7B9-9D47-45F8-82A7-57CF92B40AE6}"/>
+    <hyperlink ref="F19" r:id="rId18" xr:uid="{1CDF3FDD-8D5C-4D8A-B7EA-7044D9157508}"/>
+    <hyperlink ref="F20" r:id="rId19" xr:uid="{14C3260B-4408-49A9-B9E9-2F703BF6F6F9}"/>
+    <hyperlink ref="F21" r:id="rId20" xr:uid="{4627FC99-85B9-4D0F-9734-5866C2C43226}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{4988C40B-E086-43D7-98BB-DC44697E9D7A}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{1754B064-1700-4D24-9601-C53AEF572D87}"/>
+    <hyperlink ref="F24" r:id="rId23" xr:uid="{5D446331-F6E0-4672-AC72-962F9F0F1B29}"/>
+    <hyperlink ref="F25" r:id="rId24" xr:uid="{EEDCCC21-7A36-4CEC-8E2A-925C1A989061}"/>
+    <hyperlink ref="F26" r:id="rId25" xr:uid="{1A4FDC7F-4ADF-40E4-84A6-8488C1B5ED1B}"/>
+    <hyperlink ref="F27" r:id="rId26" xr:uid="{7A02B22A-FCDA-480A-B042-2A6A92C75B8E}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{E9F44C0A-0D54-498F-B943-49BCC0D6A66B}"/>
+    <hyperlink ref="F29" r:id="rId28" xr:uid="{DA8A2D59-CC63-45A2-9AF8-E3430601091F}"/>
+    <hyperlink ref="F30" r:id="rId29" xr:uid="{1AD35272-50C5-455E-A23D-B8A967346617}"/>
+    <hyperlink ref="F31" r:id="rId30" xr:uid="{7079BF78-9D00-4C0B-8EEC-4999871EAEE8}"/>
+    <hyperlink ref="F32" r:id="rId31" xr:uid="{67D2DD80-37E4-4FEC-9E51-3C1685E5BC43}"/>
+    <hyperlink ref="F33" r:id="rId32" xr:uid="{9E5A252A-B319-409B-A266-2B37FED906ED}"/>
+    <hyperlink ref="F34" r:id="rId33" xr:uid="{88A544E9-E678-4817-A1BD-F767EE28ADF8}"/>
+    <hyperlink ref="F35" r:id="rId34" xr:uid="{08745A87-4AC0-49F2-BDB5-AA44A162F39E}"/>
+    <hyperlink ref="F36" r:id="rId35" xr:uid="{ABE6F4AB-27D7-4A15-B58C-E85FB2A3028D}"/>
+    <hyperlink ref="F37" r:id="rId36" xr:uid="{44E9E576-7978-409C-AEDC-84847979547F}"/>
+    <hyperlink ref="F38" r:id="rId37" xr:uid="{6167F564-807E-4D36-8C1B-86F0000FB59D}"/>
+    <hyperlink ref="F39" r:id="rId38" xr:uid="{BAC1EB10-9A36-4EA0-9E94-C9893BE60FCB}"/>
+    <hyperlink ref="F40" r:id="rId39" xr:uid="{F75B2A51-6C88-43AD-BCD7-21D2FD850EF2}"/>
+    <hyperlink ref="F41" r:id="rId40" xr:uid="{A590376D-9093-472F-A083-E3700B7549F9}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{B7059D47-7A5F-4458-8CCF-B9931244947E}"/>
+    <hyperlink ref="F43" r:id="rId42" xr:uid="{D80EC979-0A8C-4F5F-BA9C-2994D0F987A0}"/>
+    <hyperlink ref="F44" r:id="rId43" xr:uid="{81663856-9204-4902-BB4D-6768E997AFBF}"/>
+    <hyperlink ref="F45" r:id="rId44" xr:uid="{4FEB0532-0F89-4AC4-821B-2A807E386D8C}"/>
+    <hyperlink ref="F46" r:id="rId45" xr:uid="{4CDDEC73-67E6-4665-9ED0-ACA312342674}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{C737C4AE-74F4-4E36-B4BC-FFC3438EE4FF}"/>
+    <hyperlink ref="F48" r:id="rId47" xr:uid="{145E2525-EF79-487C-8599-FA9252865DDA}"/>
+    <hyperlink ref="F49" r:id="rId48" xr:uid="{702DC89E-E0AB-45BA-BA10-DBABA57E482D}"/>
+    <hyperlink ref="F50" r:id="rId49" xr:uid="{D602E299-DE4A-46E2-A8FF-341D38CD7F89}"/>
+    <hyperlink ref="F51" r:id="rId50" xr:uid="{82C32BD4-9C6C-46CC-8753-ED746EEA3E59}"/>
+    <hyperlink ref="F52" r:id="rId51" xr:uid="{6D765059-A037-402D-9B93-C7113E7FCB28}"/>
+    <hyperlink ref="F53" r:id="rId52" xr:uid="{862C6F72-BAFA-489A-B3E5-38DE5A73F720}"/>
+    <hyperlink ref="F54" r:id="rId53" xr:uid="{4B0EEAA3-F37C-4E30-A18A-36601DA10DCA}"/>
+    <hyperlink ref="F55" r:id="rId54" xr:uid="{6F3010EF-BB60-4D6D-AE02-BF6DCA023096}"/>
+    <hyperlink ref="F56" r:id="rId55" xr:uid="{4441C2C8-1F28-48FD-AA5D-AD3FE82ADC0C}"/>
+    <hyperlink ref="F57" r:id="rId56" xr:uid="{A17FDA68-8854-44F0-A6FD-C706F1E0550D}"/>
+    <hyperlink ref="F58" r:id="rId57" xr:uid="{7774C242-A449-4B55-83E1-A52C901E74BE}"/>
+    <hyperlink ref="F59" r:id="rId58" xr:uid="{90FE56BB-021B-4516-A36B-18E6C11D5410}"/>
+    <hyperlink ref="F60" r:id="rId59" xr:uid="{57DA3858-8EA8-44F5-BDFC-CFCBB2B590F9}"/>
+    <hyperlink ref="F61" r:id="rId60" xr:uid="{34F7D2DD-E865-4689-87E1-F92DAE992E29}"/>
+    <hyperlink ref="F62" r:id="rId61" xr:uid="{70EA32E8-F254-4FCA-807D-CAE5618E484E}"/>
+    <hyperlink ref="F63" r:id="rId62" xr:uid="{DB681238-E671-4ADC-9FC8-109331488CBA}"/>
+    <hyperlink ref="F64" r:id="rId63" xr:uid="{F0E3D571-CE42-443A-8D36-6532A73CFBF5}"/>
+    <hyperlink ref="F65" r:id="rId64" xr:uid="{1321D6A0-6524-4C68-9158-294ED4D8305E}"/>
+    <hyperlink ref="F66" r:id="rId65" xr:uid="{EFCD9F57-5826-4898-BFD0-16E6DB5D1BCC}"/>
+    <hyperlink ref="F67" r:id="rId66" xr:uid="{53F0C385-6809-4CF0-ABA7-EEAE24DBFBC8}"/>
+    <hyperlink ref="F68" r:id="rId67" xr:uid="{D29C0DF3-1AF3-43AB-976E-3CF2B56BF6B8}"/>
+    <hyperlink ref="F69" r:id="rId68" xr:uid="{903933D9-8C01-4E08-B908-AACD99BA14B4}"/>
+    <hyperlink ref="F70" r:id="rId69" xr:uid="{6C18D706-F1CF-4502-B16E-DEFA34E50B74}"/>
+    <hyperlink ref="F71" r:id="rId70" xr:uid="{6835F774-142D-499E-87D4-1FC009762EA5}"/>
+    <hyperlink ref="F72" r:id="rId71" xr:uid="{F9FA0B8D-DC2F-4612-AA76-C503FC5F1058}"/>
+    <hyperlink ref="F73" r:id="rId72" xr:uid="{3AFB6E9B-08B5-478D-A394-B57ABB758708}"/>
+    <hyperlink ref="F74" r:id="rId73" xr:uid="{64610DFF-76EC-4E26-9945-0116D2A2EEF6}"/>
+    <hyperlink ref="F75" r:id="rId74" xr:uid="{E07CF95E-B11E-41B5-AC2B-FAE283ACBD9E}"/>
+    <hyperlink ref="F76" r:id="rId75" xr:uid="{401CB18E-A60E-4B62-B7D3-1320BD6021B5}"/>
+    <hyperlink ref="F77" r:id="rId76" xr:uid="{3F3B3AB5-F3EB-4C24-8675-BD2A54370172}"/>
+    <hyperlink ref="F78" r:id="rId77" xr:uid="{7481F5DE-8ACE-40B6-868B-6F6BE021B4F2}"/>
+    <hyperlink ref="F79" r:id="rId78" xr:uid="{1F868676-CA6E-4EBB-9205-C57E17A8881D}"/>
+    <hyperlink ref="F80" r:id="rId79" xr:uid="{326F19A9-81E5-4A08-8213-60FB341CC237}"/>
+    <hyperlink ref="F81" r:id="rId80" xr:uid="{973D8D71-60D6-4221-9881-DEE2A39496EE}"/>
+    <hyperlink ref="F82" r:id="rId81" xr:uid="{92EF883F-9A90-4DC0-94C9-CCCE6F8B1FE5}"/>
+    <hyperlink ref="F83" r:id="rId82" xr:uid="{AD073DE0-2B8C-4924-A5D5-F2827CE41C4C}"/>
+    <hyperlink ref="F84" r:id="rId83" xr:uid="{C2C2F3BE-AD69-4F5D-8857-BE1CEE596211}"/>
+    <hyperlink ref="F85" r:id="rId84" xr:uid="{B32596CE-B6AB-4C94-A517-BA97E994B327}"/>
+    <hyperlink ref="F86" r:id="rId85" xr:uid="{8CAEC33E-75F2-4E80-A7AD-EE9505F93504}"/>
+    <hyperlink ref="F87" r:id="rId86" xr:uid="{A0A94CEC-9DC9-41E2-883D-30B46A07E8C1}"/>
+    <hyperlink ref="F88" r:id="rId87" xr:uid="{9651BAA5-5B05-4F28-B7E4-4FFD51B15E17}"/>
+    <hyperlink ref="F89" r:id="rId88" xr:uid="{2DDD39F7-7C36-42B7-977F-584BBBBB6C90}"/>
+    <hyperlink ref="F90" r:id="rId89" xr:uid="{6225326A-21D8-4953-9F97-D28BFF0D8E8E}"/>
+    <hyperlink ref="F91" r:id="rId90" xr:uid="{8A97D5AE-152E-4E42-86B1-C846A7EE834E}"/>
+    <hyperlink ref="F92" r:id="rId91" xr:uid="{96572387-8B20-4687-B93D-663FFDEDFA7C}"/>
+    <hyperlink ref="F93" r:id="rId92" xr:uid="{5BA42722-CF0C-4641-9644-C798B686963E}"/>
+    <hyperlink ref="F94" r:id="rId93" xr:uid="{F6DEE3A4-C5AD-41B9-928F-CF0CDCE70D1F}"/>
+    <hyperlink ref="F95" r:id="rId94" xr:uid="{C20BEABE-75FE-42AE-B637-FD0C67BB5133}"/>
+    <hyperlink ref="F96" r:id="rId95" xr:uid="{1287DDCC-6775-4D1A-9C46-1E6835B27447}"/>
+    <hyperlink ref="F97" r:id="rId96" xr:uid="{E25623AF-36E0-4613-A9BB-D99A8F330526}"/>
+    <hyperlink ref="F98" r:id="rId97" xr:uid="{026262DF-6DB5-4744-8EBC-750C59CC68D4}"/>
+    <hyperlink ref="F99" r:id="rId98" xr:uid="{9699C2F7-A66A-4885-8AF7-0BE963BAD0FA}"/>
+    <hyperlink ref="F100" r:id="rId99" xr:uid="{3FC0CD6D-E102-4AE8-9C89-2C2ADE1E68B9}"/>
+    <hyperlink ref="F101" r:id="rId100" xr:uid="{91C79DCF-9BC1-4454-8B7D-4DF371C71DDF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N1 A3:N101 B2:E2 G2:N2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:N1 A101:E101 B2:E2 G2:N2 A3:E3 G3:N3 A4:E4 G4:N4 A5:E5 G5:N5 A6:E6 G6:N6 A7:E7 G7:N7 A8:E8 G8:N8 A9:E9 G9:N9 A10:E10 G10:N10 A11:E11 G11:N11 A12:E12 G12:N12 A13:E13 G13:N13 A14:E14 G14:N14 A15:E15 G15:N15 A16:E16 G16:N16 A17:E17 G17:N17 A18:E18 G18:N18 A19:E19 G19:N19 A20:E20 G20:N20 A21:E21 G21:N21 A22:E22 G22:N22 A23:E23 G23:N23 A24:E24 G24:N24 A25:E25 G25:N25 A26:E26 G26:N26 A27:E27 G27:N27 A28:E28 G28:N28 A29:E29 G29:N29 A30:E30 G30:N30 A31:E31 G31:N31 A32:E32 G32:N32 A33:E33 G33:N33 A34:E34 G34:N34 A35:E35 G35:N35 A36:E36 G36:N36 A37:E37 G37:N37 A38:E38 G38:N38 A39:E39 G39:N39 A40:E40 G40:N40 A41:E41 G41:N41 A42:E42 G42:N42 A43:E43 G43:N43 A44:E44 G44:N44 A45:E45 G45:N45 A46:E46 G46:N46 A47:E47 G47:N47 A48:E48 G48:N48 A49:E49 G49:N49 A50:E50 G50:N50 A51:E51 G51:N51 A52:E52 G52:N52 A53:E53 G53:N53 A54:E54 G54:N54 A55:E55 G55:N55 A56:E56 G56:N56 A57:E57 G57:N57 A58:E58 G58:N58 A59:E59 G59:N59 A60:E60 G60:N60 A61:E61 G61:N61 A62:E62 G62:N62 A63:E63 G63:N63 A64:E64 G64:N64 A65:E65 G65:N65 A66:E66 G66:N66 A67:E67 G67:N67 A68:E68 G68:N68 A69:E69 G69:N69 A70:E70 G70:N70 A71:E71 G71:N71 A72:E72 G72:N72 A73:E73 G73:N73 A74:E74 G74:N74 A75:E75 G75:N75 A76:E76 G76:N76 A77:E77 G77:N77 A78:E78 G78:N78 A79:E79 G79:N79 A80:E80 G80:N80 A81:E81 G81:N81 A82:E82 G82:N82 A83:E83 G83:N83 A84:E84 G84:N84 A85:E85 G85:N85 A86:E86 G86:N86 A87:E87 G87:N87 A88:E88 G88:N88 A89:E89 G89:N89 A90:E90 G90:N90 A91:E91 G91:N91 A92:E92 G92:N92 A93:E93 G93:N93 A94:E94 G94:N94 A95:E95 G95:N95 A96:E96 G96:N96 A97:E97 G97:N97 A98:E98 G98:N98 A99:E99 G99:N99 A100:E100 G100:N100 G101:N101" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/uploads/Sample_Products.xlsx
+++ b/backend/uploads/Sample_Products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tranm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NNPTUD_DoAn\backend\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{5EE9C431-EC15-43C7-921A-E3750169D068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -1218,7 +1218,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1226,7 +1226,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1596,12 +1596,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N101"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="130.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="130.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>83</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>106</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>109</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>119</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>121</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>124</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>127</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>129</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>132</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>134</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>136</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>141</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>144</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>147</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>150</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>152</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>154</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>156</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>159</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>162</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>164</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>169</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>172</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>174</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>177</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>179</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>181</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>184</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>186</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>188</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>190</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>192</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>195</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>197</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>199</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>201</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>203</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>206</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>208</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>210</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>213</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>215</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>217</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>220</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>223</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>225</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>227</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>229</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>231</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>233</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>235</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>238</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>243</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>245</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>247</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>249</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>251</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>253</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>255</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>257</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>259</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>261</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>264</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>267</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>270</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>272</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>274</v>
       </c>
@@ -5561,7 +5561,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>277</v>
       </c>
@@ -5605,7 +5605,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>280</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>282</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>284</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>286</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>288</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>291</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>293</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>295</v>
       </c>
@@ -5957,7 +5957,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>297</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>299</v>
       </c>
